--- a/resources/templates/Template_Confronto_Regimi_v1.0.xlsx
+++ b/resources/templates/Template_Confronto_Regimi_v1.0.xlsx
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1013,154 +1013,180 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Quota di partecipazione %</t>
+          <t>Rapporto di lavoro precedente cessato</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>nella societa professionale</t>
+          <t>SI se il rapporto e cessato e nell anno non arrivano redditi di quella natura: la soglia dei 35.000 non opera</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Utile distribuito %</t>
+          <t>Prima iscrizione alla Cassa prima dei 35 anni</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>il resto resta in societa</t>
+          <t>SI dimezza i minimi di Cassa Forense nei primi sei anni di iscrizione</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Costi di struttura della societa</t>
+          <t>Quota di partecipazione %</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>amministrazione, revisione, adempimenti</t>
+          <t>nella societa professionale</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Aliquota IRAP %</t>
+          <t>Utile distribuito %</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>da verificare per la regione</t>
+          <t>il resto resta in societa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Remunerazione dalla societa</t>
+          <t>Costi di struttura della societa</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>dividendo, compenso oppure misto</t>
+          <t>amministrazione, revisione, adempimenti</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Compenso amministratore</t>
+          <t>Aliquota IRAP %</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>lordo annuale</t>
+          <t>da verificare per la regione</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Previdenza sul compenso</t>
+          <t>Remunerazione dalla societa</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>cassa oppure inps</t>
+          <t>dividendo, compenso oppure misto</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Aliquota Gestione Separata %</t>
+          <t>Compenso amministratore</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24 oppure 33,72</t>
+          <t>lordo annuale</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Aliquota soggettiva CNPADC %</t>
+          <t>Previdenza sul compenso</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>dal 12 al 100</t>
+          <t>cassa oppure inps</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Contributo di maternita</t>
+          <t>Aliquota Gestione Separata %</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>importo fisso annuale della Cassa</t>
+          <t>24 oppure 33,72</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Addizionale regionale %</t>
+          <t>Aliquota soggettiva CNPADC %</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>da verificare per la regione</t>
+          <t>dal 12 al 100</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Addizionale comunale %</t>
+          <t>Contributo di maternita</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>importo fisso annuale della Cassa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Addizionale regionale %</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>da verificare per la regione</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Addizionale comunale %</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>da verificare per il comune</t>
         </is>

--- a/resources/templates/Template_Confronto_Regimi_v1.0.xlsx
+++ b/resources/templates/Template_Confronto_Regimi_v1.0.xlsx
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1091,102 +1091,128 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Remunerazione dalla societa</t>
+          <t>Modalita di calcolo della societa</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>dividendo, compenso oppure misto</t>
+          <t>automatico oppure manuale: in automatico il tool cerca il mix migliore fra compenso e dividendo</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Compenso amministratore</t>
+          <t>Quanto deve restare in societa</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>lordo annuale</t>
+          <t>vincolo per l ottimizzazione: capitale circolante, investimenti</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Previdenza sul compenso</t>
+          <t>Remunerazione dalla societa</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>cassa oppure inps</t>
+          <t>solo in manuale: dividendo, compenso oppure misto</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Aliquota Gestione Separata %</t>
+          <t>Compenso amministratore</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24 oppure 33,72</t>
+          <t>lordo annuale</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Aliquota soggettiva CNPADC %</t>
+          <t>Previdenza sul compenso</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>dal 12 al 100</t>
+          <t>cassa oppure inps</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Contributo di maternita</t>
+          <t>Aliquota Gestione Separata %</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>importo fisso annuale della Cassa</t>
+          <t>24 oppure 33,72</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Addizionale regionale %</t>
+          <t>Aliquota soggettiva CNPADC %</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>da verificare per la regione</t>
+          <t>dal 12 al 100</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Addizionale comunale %</t>
+          <t>Contributo di maternita</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>importo fisso annuale della Cassa</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Addizionale regionale %</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>da verificare per la regione</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Addizionale comunale %</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>da verificare per il comune</t>
         </is>
